--- a/LubanTables/Datas/grid_plane.xlsx
+++ b/LubanTables/Datas/grid_plane.xlsx
@@ -1154,10 +1154,10 @@
         <v>1001</v>
       </c>
       <c r="D5" s="0">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E5" s="0">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F5" s="0">
         <v>1</v>
@@ -1168,10 +1168,10 @@
         <v>1002</v>
       </c>
       <c r="D6" s="0">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="E6" s="0">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="F6" s="0">
         <v>1</v>
